--- a/data/tags/סינגלים חדשים/global/2026-02-week02/titles.xlsx
+++ b/data/tags/סינגלים חדשים/global/2026-02-week02/titles.xlsx
@@ -397,7 +397,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:L2"/>
+  <dimension ref="A1:L7"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -436,13 +436,13 @@
     </row>
     <row r="2">
       <c r="A2" t="str">
-        <v>יובל בנשלום – ממשיך ליפול</v>
+        <v>ליעד מאיר - חברים שלי</v>
       </c>
       <c r="B2" t="str">
         <v>2026-02-08</v>
       </c>
       <c r="C2" t="str">
-        <v>https://yosmusic.com/%d7%99%d7%95%d7%91%d7%9c-%d7%91%d7%a0%d7%a9%d7%9c%d7%95%d7%9d-%d7%9e%d7%9e%d7%a9%d7%99%d7%9a-%d7%9c%d7%99%d7%a4%d7%95%d7%9c/</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409539&amp;sid=87f6560e4cca73536893ba8ad3945b18</v>
       </c>
       <c r="D2" t="str">
         <v>2026-02-08</v>
@@ -451,7 +451,7 @@
         <v/>
       </c>
       <c r="F2" t="str">
-        <v>יובל בנשלום שר שיר עדין קשה, שכוחו נובע דווקא מהעובדה שהוא לא מנסה לפתור את הדיכאון – אלא להיות לידו. זהו שיר על אהבה תחת דיכאון, נאמנות של אוהבת שלא יודעת איך לעזור, פער כואב בין רצון למציאות הבחירה לספר</v>
+        <v/>
       </c>
       <c r="G2" t="str">
         <v/>
@@ -469,12 +469,202 @@
         <v/>
       </c>
       <c r="L2" t="str">
-        <v>יובל בנשלום – ממשיך ליפול</v>
+        <v>ליעד מאיר - חברים שלי</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="str">
+        <v>ליאור עמדי - חן הבה</v>
+      </c>
+      <c r="B3" t="str">
+        <v>2026-02-08</v>
+      </c>
+      <c r="C3" t="str">
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409538&amp;sid=87f6560e4cca73536893ba8ad3945b18</v>
+      </c>
+      <c r="D3" t="str">
+        <v>2026-02-08</v>
+      </c>
+      <c r="E3" t="str">
+        <v/>
+      </c>
+      <c r="F3" t="str">
+        <v/>
+      </c>
+      <c r="G3" t="str">
+        <v/>
+      </c>
+      <c r="H3" t="str">
+        <v/>
+      </c>
+      <c r="I3" t="str">
+        <v>סינגלים חדשים</v>
+      </c>
+      <c r="J3" t="str">
+        <v/>
+      </c>
+      <c r="K3" t="str">
+        <v/>
+      </c>
+      <c r="L3" t="str">
+        <v>ליאור עמדי - חן הבה</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="str">
+        <v>יגל יובל שרעבי - אלופו של עולם</v>
+      </c>
+      <c r="B4" t="str">
+        <v>2026-02-08</v>
+      </c>
+      <c r="C4" t="str">
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409537&amp;sid=87f6560e4cca73536893ba8ad3945b18</v>
+      </c>
+      <c r="D4" t="str">
+        <v>2026-02-08</v>
+      </c>
+      <c r="E4" t="str">
+        <v/>
+      </c>
+      <c r="F4" t="str">
+        <v/>
+      </c>
+      <c r="G4" t="str">
+        <v/>
+      </c>
+      <c r="H4" t="str">
+        <v/>
+      </c>
+      <c r="I4" t="str">
+        <v>סינגלים חדשים</v>
+      </c>
+      <c r="J4" t="str">
+        <v/>
+      </c>
+      <c r="K4" t="str">
+        <v/>
+      </c>
+      <c r="L4" t="str">
+        <v>יגל יובל שרעבי - אלופו של עולם</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="str">
+        <v>טלי רבקה סימן טוב - אני עץ, אני אילן</v>
+      </c>
+      <c r="B5" t="str">
+        <v>2026-02-08</v>
+      </c>
+      <c r="C5" t="str">
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409536&amp;sid=87f6560e4cca73536893ba8ad3945b18</v>
+      </c>
+      <c r="D5" t="str">
+        <v>2026-02-08</v>
+      </c>
+      <c r="E5" t="str">
+        <v/>
+      </c>
+      <c r="F5" t="str">
+        <v/>
+      </c>
+      <c r="G5" t="str">
+        <v/>
+      </c>
+      <c r="H5" t="str">
+        <v/>
+      </c>
+      <c r="I5" t="str">
+        <v>סינגלים חדשים</v>
+      </c>
+      <c r="J5" t="str">
+        <v/>
+      </c>
+      <c r="K5" t="str">
+        <v/>
+      </c>
+      <c r="L5" t="str">
+        <v>טלי רבקה סימן טוב - אני עץ, אני אילן</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="str">
+        <v>חיים ישראל - מחרוזת השירים של זוהר 2026</v>
+      </c>
+      <c r="B6" t="str">
+        <v>2026-02-08</v>
+      </c>
+      <c r="C6" t="str">
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409535&amp;sid=87f6560e4cca73536893ba8ad3945b18</v>
+      </c>
+      <c r="D6" t="str">
+        <v>2026-02-08</v>
+      </c>
+      <c r="E6" t="str">
+        <v/>
+      </c>
+      <c r="F6" t="str">
+        <v/>
+      </c>
+      <c r="G6" t="str">
+        <v/>
+      </c>
+      <c r="H6" t="str">
+        <v/>
+      </c>
+      <c r="I6" t="str">
+        <v>סינגלים חדשים</v>
+      </c>
+      <c r="J6" t="str">
+        <v/>
+      </c>
+      <c r="K6" t="str">
+        <v/>
+      </c>
+      <c r="L6" t="str">
+        <v>חיים ישראל - מחרוזת השירים של זוהר 2026</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="str">
+        <v>האחים דוליס - הלילה עבר</v>
+      </c>
+      <c r="B7" t="str">
+        <v>2026-02-08</v>
+      </c>
+      <c r="C7" t="str">
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409534&amp;sid=87f6560e4cca73536893ba8ad3945b18</v>
+      </c>
+      <c r="D7" t="str">
+        <v>2026-02-08</v>
+      </c>
+      <c r="E7" t="str">
+        <v/>
+      </c>
+      <c r="F7" t="str">
+        <v/>
+      </c>
+      <c r="G7" t="str">
+        <v/>
+      </c>
+      <c r="H7" t="str">
+        <v/>
+      </c>
+      <c r="I7" t="str">
+        <v>סינגלים חדשים</v>
+      </c>
+      <c r="J7" t="str">
+        <v/>
+      </c>
+      <c r="K7" t="str">
+        <v/>
+      </c>
+      <c r="L7" t="str">
+        <v>האחים דוליס - הלילה עבר</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:L2"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:L7"/>
   </ignoredErrors>
 </worksheet>
 </file>
--- a/data/tags/סינגלים חדשים/global/2026-02-week02/titles.xlsx
+++ b/data/tags/סינגלים חדשים/global/2026-02-week02/titles.xlsx
@@ -397,7 +397,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:L7"/>
+  <dimension ref="A1:L5"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -436,13 +436,13 @@
     </row>
     <row r="2">
       <c r="A2" t="str">
-        <v>ליעד מאיר - חברים שלי</v>
+        <v>צח חכים &amp; להקת רגעים - מחרוזת שבת 2026</v>
       </c>
       <c r="B2" t="str">
         <v>2026-02-08</v>
       </c>
       <c r="C2" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409539&amp;sid=87f6560e4cca73536893ba8ad3945b18</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409543&amp;sid=26f889f6709bd4f04695b840d70c4020</v>
       </c>
       <c r="D2" t="str">
         <v>2026-02-08</v>
@@ -469,18 +469,18 @@
         <v/>
       </c>
       <c r="L2" t="str">
-        <v>ליעד מאיר - חברים שלי</v>
+        <v>צח חכים &amp; להקת רגעים - מחרוזת שבת 2026</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="str">
-        <v>ליאור עמדי - חן הבה</v>
+        <v>סדיאל בכר - אי אפשר להסביר</v>
       </c>
       <c r="B3" t="str">
         <v>2026-02-08</v>
       </c>
       <c r="C3" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409538&amp;sid=87f6560e4cca73536893ba8ad3945b18</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409542&amp;sid=26f889f6709bd4f04695b840d70c4020</v>
       </c>
       <c r="D3" t="str">
         <v>2026-02-08</v>
@@ -507,18 +507,18 @@
         <v/>
       </c>
       <c r="L3" t="str">
-        <v>ליאור עמדי - חן הבה</v>
+        <v>סדיאל בכר - אי אפשר להסביר</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="str">
-        <v>יגל יובל שרעבי - אלופו של עולם</v>
+        <v>ניר קלברס - סיגריה בסלון</v>
       </c>
       <c r="B4" t="str">
         <v>2026-02-08</v>
       </c>
       <c r="C4" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409537&amp;sid=87f6560e4cca73536893ba8ad3945b18</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409541&amp;sid=26f889f6709bd4f04695b840d70c4020</v>
       </c>
       <c r="D4" t="str">
         <v>2026-02-08</v>
@@ -545,18 +545,18 @@
         <v/>
       </c>
       <c r="L4" t="str">
-        <v>יגל יובל שרעבי - אלופו של עולם</v>
+        <v>ניר קלברס - סיגריה בסלון</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="str">
-        <v>טלי רבקה סימן טוב - אני עץ, אני אילן</v>
+        <v>מאור יפרח - אין עוד מלבדך</v>
       </c>
       <c r="B5" t="str">
         <v>2026-02-08</v>
       </c>
       <c r="C5" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409536&amp;sid=87f6560e4cca73536893ba8ad3945b18</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409540&amp;sid=26f889f6709bd4f04695b840d70c4020</v>
       </c>
       <c r="D5" t="str">
         <v>2026-02-08</v>
@@ -583,88 +583,12 @@
         <v/>
       </c>
       <c r="L5" t="str">
-        <v>טלי רבקה סימן טוב - אני עץ, אני אילן</v>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" t="str">
-        <v>חיים ישראל - מחרוזת השירים של זוהר 2026</v>
-      </c>
-      <c r="B6" t="str">
-        <v>2026-02-08</v>
-      </c>
-      <c r="C6" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409535&amp;sid=87f6560e4cca73536893ba8ad3945b18</v>
-      </c>
-      <c r="D6" t="str">
-        <v>2026-02-08</v>
-      </c>
-      <c r="E6" t="str">
-        <v/>
-      </c>
-      <c r="F6" t="str">
-        <v/>
-      </c>
-      <c r="G6" t="str">
-        <v/>
-      </c>
-      <c r="H6" t="str">
-        <v/>
-      </c>
-      <c r="I6" t="str">
-        <v>סינגלים חדשים</v>
-      </c>
-      <c r="J6" t="str">
-        <v/>
-      </c>
-      <c r="K6" t="str">
-        <v/>
-      </c>
-      <c r="L6" t="str">
-        <v>חיים ישראל - מחרוזת השירים של זוהר 2026</v>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" t="str">
-        <v>האחים דוליס - הלילה עבר</v>
-      </c>
-      <c r="B7" t="str">
-        <v>2026-02-08</v>
-      </c>
-      <c r="C7" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409534&amp;sid=87f6560e4cca73536893ba8ad3945b18</v>
-      </c>
-      <c r="D7" t="str">
-        <v>2026-02-08</v>
-      </c>
-      <c r="E7" t="str">
-        <v/>
-      </c>
-      <c r="F7" t="str">
-        <v/>
-      </c>
-      <c r="G7" t="str">
-        <v/>
-      </c>
-      <c r="H7" t="str">
-        <v/>
-      </c>
-      <c r="I7" t="str">
-        <v>סינגלים חדשים</v>
-      </c>
-      <c r="J7" t="str">
-        <v/>
-      </c>
-      <c r="K7" t="str">
-        <v/>
-      </c>
-      <c r="L7" t="str">
-        <v>האחים דוליס - הלילה עבר</v>
+        <v>מאור יפרח - אין עוד מלבדך</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:L7"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:L5"/>
   </ignoredErrors>
 </worksheet>
 </file>
--- a/data/tags/סינגלים חדשים/global/2026-02-week02/titles.xlsx
+++ b/data/tags/סינגלים חדשים/global/2026-02-week02/titles.xlsx
@@ -397,7 +397,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:L5"/>
+  <dimension ref="A1:L2"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -436,22 +436,22 @@
     </row>
     <row r="2">
       <c r="A2" t="str">
-        <v>צח חכים &amp; להקת רגעים - מחרוזת שבת 2026</v>
+        <v>מייפל Wishing for peace</v>
       </c>
       <c r="B2" t="str">
-        <v>2026-02-08</v>
+        <v>2026-02-09</v>
       </c>
       <c r="C2" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409543&amp;sid=26f889f6709bd4f04695b840d70c4020</v>
+        <v>https://yosmusic.com/%d7%9e%d7%99%d7%99%d7%a4%d7%9c-wishing-for-peace/</v>
       </c>
       <c r="D2" t="str">
-        <v>2026-02-08</v>
+        <v>2026-02-09</v>
       </c>
       <c r="E2" t="str">
         <v/>
       </c>
       <c r="F2" t="str">
-        <v/>
+        <v>מייפל שרה שיר בעל משקל היסטורי ורגשי עצום. “Wishing for Peace” הוא שיר פולק, שנולד מעדות משפחתית. הבחירה בבלדת פולק מיד־טמפו איננה מקרית. פולק הוא ז’אנר של סיפורים, מסורת והעברה בין דורות. הקצב האמצעי מתניע דרמה. של הליכה מתמשכת זו</v>
       </c>
       <c r="G2" t="str">
         <v/>
@@ -469,126 +469,12 @@
         <v/>
       </c>
       <c r="L2" t="str">
-        <v>צח חכים &amp; להקת רגעים - מחרוזת שבת 2026</v>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" t="str">
-        <v>סדיאל בכר - אי אפשר להסביר</v>
-      </c>
-      <c r="B3" t="str">
-        <v>2026-02-08</v>
-      </c>
-      <c r="C3" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409542&amp;sid=26f889f6709bd4f04695b840d70c4020</v>
-      </c>
-      <c r="D3" t="str">
-        <v>2026-02-08</v>
-      </c>
-      <c r="E3" t="str">
-        <v/>
-      </c>
-      <c r="F3" t="str">
-        <v/>
-      </c>
-      <c r="G3" t="str">
-        <v/>
-      </c>
-      <c r="H3" t="str">
-        <v/>
-      </c>
-      <c r="I3" t="str">
-        <v>סינגלים חדשים</v>
-      </c>
-      <c r="J3" t="str">
-        <v/>
-      </c>
-      <c r="K3" t="str">
-        <v/>
-      </c>
-      <c r="L3" t="str">
-        <v>סדיאל בכר - אי אפשר להסביר</v>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="str">
-        <v>ניר קלברס - סיגריה בסלון</v>
-      </c>
-      <c r="B4" t="str">
-        <v>2026-02-08</v>
-      </c>
-      <c r="C4" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409541&amp;sid=26f889f6709bd4f04695b840d70c4020</v>
-      </c>
-      <c r="D4" t="str">
-        <v>2026-02-08</v>
-      </c>
-      <c r="E4" t="str">
-        <v/>
-      </c>
-      <c r="F4" t="str">
-        <v/>
-      </c>
-      <c r="G4" t="str">
-        <v/>
-      </c>
-      <c r="H4" t="str">
-        <v/>
-      </c>
-      <c r="I4" t="str">
-        <v>סינגלים חדשים</v>
-      </c>
-      <c r="J4" t="str">
-        <v/>
-      </c>
-      <c r="K4" t="str">
-        <v/>
-      </c>
-      <c r="L4" t="str">
-        <v>ניר קלברס - סיגריה בסלון</v>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" t="str">
-        <v>מאור יפרח - אין עוד מלבדך</v>
-      </c>
-      <c r="B5" t="str">
-        <v>2026-02-08</v>
-      </c>
-      <c r="C5" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409540&amp;sid=26f889f6709bd4f04695b840d70c4020</v>
-      </c>
-      <c r="D5" t="str">
-        <v>2026-02-08</v>
-      </c>
-      <c r="E5" t="str">
-        <v/>
-      </c>
-      <c r="F5" t="str">
-        <v/>
-      </c>
-      <c r="G5" t="str">
-        <v/>
-      </c>
-      <c r="H5" t="str">
-        <v/>
-      </c>
-      <c r="I5" t="str">
-        <v>סינגלים חדשים</v>
-      </c>
-      <c r="J5" t="str">
-        <v/>
-      </c>
-      <c r="K5" t="str">
-        <v/>
-      </c>
-      <c r="L5" t="str">
-        <v>מאור יפרח - אין עוד מלבדך</v>
+        <v>מייפל Wishing for peace</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:L5"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:L2"/>
   </ignoredErrors>
 </worksheet>
 </file>
--- a/data/tags/סינגלים חדשים/global/2026-02-week02/titles.xlsx
+++ b/data/tags/סינגלים חדשים/global/2026-02-week02/titles.xlsx
@@ -436,13 +436,13 @@
     </row>
     <row r="2">
       <c r="A2" t="str">
-        <v>מייפל Wishing for peace</v>
+        <v>אליעד ולירון עמרם – עוד שבוע</v>
       </c>
       <c r="B2" t="str">
         <v>2026-02-09</v>
       </c>
       <c r="C2" t="str">
-        <v>https://yosmusic.com/%d7%9e%d7%99%d7%99%d7%a4%d7%9c-wishing-for-peace/</v>
+        <v>https://yosmusic.com/%d7%90%d7%9c%d7%99%d7%a2%d7%93-%d7%95%d7%9c%d7%99%d7%a8%d7%95%d7%9f-%d7%a2%d7%9e%d7%a8%d7%9d-%d7%a2%d7%95%d7%93-%d7%a9%d7%91%d7%95%d7%a2/</v>
       </c>
       <c r="D2" t="str">
         <v>2026-02-09</v>
@@ -451,7 +451,7 @@
         <v/>
       </c>
       <c r="F2" t="str">
-        <v>מייפל שרה שיר בעל משקל היסטורי ורגשי עצום. “Wishing for Peace” הוא שיר פולק, שנולד מעדות משפחתית. הבחירה בבלדת פולק מיד־טמפו איננה מקרית. פולק הוא ז’אנר של סיפורים, מסורת והעברה בין דורות. הקצב האמצעי מתניע דרמה. של הליכה מתמשכת זו</v>
+        <v>הלב של השיר הוא רעיון אחד, שחוזר שוב ושוב: הזמן לא זז בלעדיה. ראשון שני שלישי והימים כבר לא עוברים אצלו. זהו תיאור  קלישאתי שאומר אכזריות הזמן – ספירת ימים, תלישת דפים, שעון, שבתות וחגים. הכול מוכר, הכול עובד, אבל</v>
       </c>
       <c r="G2" t="str">
         <v/>
@@ -469,7 +469,7 @@
         <v/>
       </c>
       <c r="L2" t="str">
-        <v>מייפל Wishing for peace</v>
+        <v>אליעד ולירון עמרם – עוד שבוע</v>
       </c>
     </row>
   </sheetData>

--- a/data/tags/סינגלים חדשים/global/2026-02-week02/titles.xlsx
+++ b/data/tags/סינגלים חדשים/global/2026-02-week02/titles.xlsx
@@ -397,7 +397,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:L2"/>
+  <dimension ref="A1:L10"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -436,13 +436,13 @@
     </row>
     <row r="2">
       <c r="A2" t="str">
-        <v>אליעד ולירון עמרם – עוד שבוע</v>
+        <v>ששון שאולוב - המונית העצובה</v>
       </c>
       <c r="B2" t="str">
         <v>2026-02-09</v>
       </c>
       <c r="C2" t="str">
-        <v>https://yosmusic.com/%d7%90%d7%9c%d7%99%d7%a2%d7%93-%d7%95%d7%9c%d7%99%d7%a8%d7%95%d7%9f-%d7%a2%d7%9e%d7%a8%d7%9d-%d7%a2%d7%95%d7%93-%d7%a9%d7%91%d7%95%d7%a2/</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409551&amp;sid=a2e881787d5869f0ba0591995121c6bf</v>
       </c>
       <c r="D2" t="str">
         <v>2026-02-09</v>
@@ -451,7 +451,7 @@
         <v/>
       </c>
       <c r="F2" t="str">
-        <v>הלב של השיר הוא רעיון אחד, שחוזר שוב ושוב: הזמן לא זז בלעדיה. ראשון שני שלישי והימים כבר לא עוברים אצלו. זהו תיאור  קלישאתי שאומר אכזריות הזמן – ספירת ימים, תלישת דפים, שעון, שבתות וחגים. הכול מוכר, הכול עובד, אבל</v>
+        <v/>
       </c>
       <c r="G2" t="str">
         <v/>
@@ -469,12 +469,316 @@
         <v/>
       </c>
       <c r="L2" t="str">
-        <v>אליעד ולירון עמרם – עוד שבוע</v>
+        <v>ששון שאולוב - המונית העצובה</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="str">
+        <v>רומי קוגן - מסיבה של מחשבות</v>
+      </c>
+      <c r="B3" t="str">
+        <v>2026-02-09</v>
+      </c>
+      <c r="C3" t="str">
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409550&amp;sid=a2e881787d5869f0ba0591995121c6bf</v>
+      </c>
+      <c r="D3" t="str">
+        <v>2026-02-09</v>
+      </c>
+      <c r="E3" t="str">
+        <v/>
+      </c>
+      <c r="F3" t="str">
+        <v/>
+      </c>
+      <c r="G3" t="str">
+        <v/>
+      </c>
+      <c r="H3" t="str">
+        <v/>
+      </c>
+      <c r="I3" t="str">
+        <v>סינגלים חדשים</v>
+      </c>
+      <c r="J3" t="str">
+        <v/>
+      </c>
+      <c r="K3" t="str">
+        <v/>
+      </c>
+      <c r="L3" t="str">
+        <v>רומי קוגן - מסיבה של מחשבות</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="str">
+        <v>משה כורסיה - עומד מולך היום</v>
+      </c>
+      <c r="B4" t="str">
+        <v>2026-02-09</v>
+      </c>
+      <c r="C4" t="str">
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409549&amp;sid=a2e881787d5869f0ba0591995121c6bf</v>
+      </c>
+      <c r="D4" t="str">
+        <v>2026-02-09</v>
+      </c>
+      <c r="E4" t="str">
+        <v/>
+      </c>
+      <c r="F4" t="str">
+        <v/>
+      </c>
+      <c r="G4" t="str">
+        <v/>
+      </c>
+      <c r="H4" t="str">
+        <v/>
+      </c>
+      <c r="I4" t="str">
+        <v>סינגלים חדשים</v>
+      </c>
+      <c r="J4" t="str">
+        <v/>
+      </c>
+      <c r="K4" t="str">
+        <v/>
+      </c>
+      <c r="L4" t="str">
+        <v>משה כורסיה - עומד מולך היום</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="str">
+        <v>יהודה בוחבוט - אלף גלגולים</v>
+      </c>
+      <c r="B5" t="str">
+        <v>2026-02-09</v>
+      </c>
+      <c r="C5" t="str">
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409548&amp;sid=a2e881787d5869f0ba0591995121c6bf</v>
+      </c>
+      <c r="D5" t="str">
+        <v>2026-02-09</v>
+      </c>
+      <c r="E5" t="str">
+        <v/>
+      </c>
+      <c r="F5" t="str">
+        <v/>
+      </c>
+      <c r="G5" t="str">
+        <v/>
+      </c>
+      <c r="H5" t="str">
+        <v/>
+      </c>
+      <c r="I5" t="str">
+        <v>סינגלים חדשים</v>
+      </c>
+      <c r="J5" t="str">
+        <v/>
+      </c>
+      <c r="K5" t="str">
+        <v/>
+      </c>
+      <c r="L5" t="str">
+        <v>יהודה בוחבוט - אלף גלגולים</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="str">
+        <v>דוד פילס - אהבה יוונית</v>
+      </c>
+      <c r="B6" t="str">
+        <v>2026-02-09</v>
+      </c>
+      <c r="C6" t="str">
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409547&amp;sid=a2e881787d5869f0ba0591995121c6bf</v>
+      </c>
+      <c r="D6" t="str">
+        <v>2026-02-09</v>
+      </c>
+      <c r="E6" t="str">
+        <v/>
+      </c>
+      <c r="F6" t="str">
+        <v/>
+      </c>
+      <c r="G6" t="str">
+        <v/>
+      </c>
+      <c r="H6" t="str">
+        <v/>
+      </c>
+      <c r="I6" t="str">
+        <v>סינגלים חדשים</v>
+      </c>
+      <c r="J6" t="str">
+        <v/>
+      </c>
+      <c r="K6" t="str">
+        <v/>
+      </c>
+      <c r="L6" t="str">
+        <v>דוד פילס - אהבה יוונית</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="str">
+        <v>אניה בוקשטיין - רק עכשיו</v>
+      </c>
+      <c r="B7" t="str">
+        <v>2026-02-09</v>
+      </c>
+      <c r="C7" t="str">
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409546&amp;sid=a2e881787d5869f0ba0591995121c6bf</v>
+      </c>
+      <c r="D7" t="str">
+        <v>2026-02-09</v>
+      </c>
+      <c r="E7" t="str">
+        <v/>
+      </c>
+      <c r="F7" t="str">
+        <v/>
+      </c>
+      <c r="G7" t="str">
+        <v/>
+      </c>
+      <c r="H7" t="str">
+        <v/>
+      </c>
+      <c r="I7" t="str">
+        <v>סינגלים חדשים</v>
+      </c>
+      <c r="J7" t="str">
+        <v/>
+      </c>
+      <c r="K7" t="str">
+        <v/>
+      </c>
+      <c r="L7" t="str">
+        <v>אניה בוקשטיין - רק עכשיו</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="str">
+        <v>אליעד &amp; לירון עמרם - עוד שבוע</v>
+      </c>
+      <c r="B8" t="str">
+        <v>2026-02-09</v>
+      </c>
+      <c r="C8" t="str">
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409545&amp;sid=a2e881787d5869f0ba0591995121c6bf</v>
+      </c>
+      <c r="D8" t="str">
+        <v>2026-02-09</v>
+      </c>
+      <c r="E8" t="str">
+        <v/>
+      </c>
+      <c r="F8" t="str">
+        <v/>
+      </c>
+      <c r="G8" t="str">
+        <v/>
+      </c>
+      <c r="H8" t="str">
+        <v/>
+      </c>
+      <c r="I8" t="str">
+        <v>סינגלים חדשים</v>
+      </c>
+      <c r="J8" t="str">
+        <v/>
+      </c>
+      <c r="K8" t="str">
+        <v/>
+      </c>
+      <c r="L8" t="str">
+        <v>אליעד &amp; לירון עמרם - עוד שבוע</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="str">
+        <v>אביה שרמן &amp; אביעד - משיח</v>
+      </c>
+      <c r="B9" t="str">
+        <v>2026-02-09</v>
+      </c>
+      <c r="C9" t="str">
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409544&amp;sid=a2e881787d5869f0ba0591995121c6bf</v>
+      </c>
+      <c r="D9" t="str">
+        <v>2026-02-09</v>
+      </c>
+      <c r="E9" t="str">
+        <v/>
+      </c>
+      <c r="F9" t="str">
+        <v/>
+      </c>
+      <c r="G9" t="str">
+        <v/>
+      </c>
+      <c r="H9" t="str">
+        <v/>
+      </c>
+      <c r="I9" t="str">
+        <v>סינגלים חדשים</v>
+      </c>
+      <c r="J9" t="str">
+        <v/>
+      </c>
+      <c r="K9" t="str">
+        <v/>
+      </c>
+      <c r="L9" t="str">
+        <v>אביה שרמן &amp; אביעד - משיח</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="str">
+        <v>מיסטר הבי ומיס לואו – Not everything you wanted</v>
+      </c>
+      <c r="B10" t="str">
+        <v>2026-02-09</v>
+      </c>
+      <c r="C10" t="str">
+        <v>https://yosmusic.com/%d7%9e%d7%99%d7%a1%d7%98%d7%a8-%d7%94%d7%91%d7%99-%d7%95%d7%9e%d7%99%d7%a1-%d7%9c%d7%95%d7%90%d7%95-not-everything-you-wanted/</v>
+      </c>
+      <c r="D10" t="str">
+        <v>2026-02-09</v>
+      </c>
+      <c r="E10" t="str">
+        <v/>
+      </c>
+      <c r="F10" t="str">
+        <v>. “Not Everything You Wanted” של מיסטר הבי אנד מיס לואו (Mr. Heavy &amp; Ms. Low) הוא שיר מעבר  לא רק גיאוגרפי (עיר-כפר), אלא קיומי. שיר על בחירה שמכילה ויתור, אימהות בלי אידיאליזציה, חיים כפריים כמרחב של גילוי, לא של</v>
+      </c>
+      <c r="G10" t="str">
+        <v/>
+      </c>
+      <c r="H10" t="str">
+        <v/>
+      </c>
+      <c r="I10" t="str">
+        <v>סינגלים חדשים</v>
+      </c>
+      <c r="J10" t="str">
+        <v/>
+      </c>
+      <c r="K10" t="str">
+        <v/>
+      </c>
+      <c r="L10" t="str">
+        <v>מיסטר הבי ומיס לואו – Not everything you wanted</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:L2"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:L10"/>
   </ignoredErrors>
 </worksheet>
 </file>
--- a/data/tags/סינגלים חדשים/global/2026-02-week02/titles.xlsx
+++ b/data/tags/סינגלים חדשים/global/2026-02-week02/titles.xlsx
@@ -397,7 +397,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:L10"/>
+  <dimension ref="A1:L2"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -436,13 +436,13 @@
     </row>
     <row r="2">
       <c r="A2" t="str">
-        <v>ששון שאולוב - המונית העצובה</v>
+        <v>איציק קלה &amp; יובל טייב - רפאני</v>
       </c>
       <c r="B2" t="str">
         <v>2026-02-09</v>
       </c>
       <c r="C2" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409551&amp;sid=a2e881787d5869f0ba0591995121c6bf</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=383792&amp;sid=adb305d69ff5373f52ea1464f61a4067</v>
       </c>
       <c r="D2" t="str">
         <v>2026-02-09</v>
@@ -469,316 +469,12 @@
         <v/>
       </c>
       <c r="L2" t="str">
-        <v>ששון שאולוב - המונית העצובה</v>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" t="str">
-        <v>רומי קוגן - מסיבה של מחשבות</v>
-      </c>
-      <c r="B3" t="str">
-        <v>2026-02-09</v>
-      </c>
-      <c r="C3" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409550&amp;sid=a2e881787d5869f0ba0591995121c6bf</v>
-      </c>
-      <c r="D3" t="str">
-        <v>2026-02-09</v>
-      </c>
-      <c r="E3" t="str">
-        <v/>
-      </c>
-      <c r="F3" t="str">
-        <v/>
-      </c>
-      <c r="G3" t="str">
-        <v/>
-      </c>
-      <c r="H3" t="str">
-        <v/>
-      </c>
-      <c r="I3" t="str">
-        <v>סינגלים חדשים</v>
-      </c>
-      <c r="J3" t="str">
-        <v/>
-      </c>
-      <c r="K3" t="str">
-        <v/>
-      </c>
-      <c r="L3" t="str">
-        <v>רומי קוגן - מסיבה של מחשבות</v>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="str">
-        <v>משה כורסיה - עומד מולך היום</v>
-      </c>
-      <c r="B4" t="str">
-        <v>2026-02-09</v>
-      </c>
-      <c r="C4" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409549&amp;sid=a2e881787d5869f0ba0591995121c6bf</v>
-      </c>
-      <c r="D4" t="str">
-        <v>2026-02-09</v>
-      </c>
-      <c r="E4" t="str">
-        <v/>
-      </c>
-      <c r="F4" t="str">
-        <v/>
-      </c>
-      <c r="G4" t="str">
-        <v/>
-      </c>
-      <c r="H4" t="str">
-        <v/>
-      </c>
-      <c r="I4" t="str">
-        <v>סינגלים חדשים</v>
-      </c>
-      <c r="J4" t="str">
-        <v/>
-      </c>
-      <c r="K4" t="str">
-        <v/>
-      </c>
-      <c r="L4" t="str">
-        <v>משה כורסיה - עומד מולך היום</v>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" t="str">
-        <v>יהודה בוחבוט - אלף גלגולים</v>
-      </c>
-      <c r="B5" t="str">
-        <v>2026-02-09</v>
-      </c>
-      <c r="C5" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409548&amp;sid=a2e881787d5869f0ba0591995121c6bf</v>
-      </c>
-      <c r="D5" t="str">
-        <v>2026-02-09</v>
-      </c>
-      <c r="E5" t="str">
-        <v/>
-      </c>
-      <c r="F5" t="str">
-        <v/>
-      </c>
-      <c r="G5" t="str">
-        <v/>
-      </c>
-      <c r="H5" t="str">
-        <v/>
-      </c>
-      <c r="I5" t="str">
-        <v>סינגלים חדשים</v>
-      </c>
-      <c r="J5" t="str">
-        <v/>
-      </c>
-      <c r="K5" t="str">
-        <v/>
-      </c>
-      <c r="L5" t="str">
-        <v>יהודה בוחבוט - אלף גלגולים</v>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" t="str">
-        <v>דוד פילס - אהבה יוונית</v>
-      </c>
-      <c r="B6" t="str">
-        <v>2026-02-09</v>
-      </c>
-      <c r="C6" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409547&amp;sid=a2e881787d5869f0ba0591995121c6bf</v>
-      </c>
-      <c r="D6" t="str">
-        <v>2026-02-09</v>
-      </c>
-      <c r="E6" t="str">
-        <v/>
-      </c>
-      <c r="F6" t="str">
-        <v/>
-      </c>
-      <c r="G6" t="str">
-        <v/>
-      </c>
-      <c r="H6" t="str">
-        <v/>
-      </c>
-      <c r="I6" t="str">
-        <v>סינגלים חדשים</v>
-      </c>
-      <c r="J6" t="str">
-        <v/>
-      </c>
-      <c r="K6" t="str">
-        <v/>
-      </c>
-      <c r="L6" t="str">
-        <v>דוד פילס - אהבה יוונית</v>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" t="str">
-        <v>אניה בוקשטיין - רק עכשיו</v>
-      </c>
-      <c r="B7" t="str">
-        <v>2026-02-09</v>
-      </c>
-      <c r="C7" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409546&amp;sid=a2e881787d5869f0ba0591995121c6bf</v>
-      </c>
-      <c r="D7" t="str">
-        <v>2026-02-09</v>
-      </c>
-      <c r="E7" t="str">
-        <v/>
-      </c>
-      <c r="F7" t="str">
-        <v/>
-      </c>
-      <c r="G7" t="str">
-        <v/>
-      </c>
-      <c r="H7" t="str">
-        <v/>
-      </c>
-      <c r="I7" t="str">
-        <v>סינגלים חדשים</v>
-      </c>
-      <c r="J7" t="str">
-        <v/>
-      </c>
-      <c r="K7" t="str">
-        <v/>
-      </c>
-      <c r="L7" t="str">
-        <v>אניה בוקשטיין - רק עכשיו</v>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" t="str">
-        <v>אליעד &amp; לירון עמרם - עוד שבוע</v>
-      </c>
-      <c r="B8" t="str">
-        <v>2026-02-09</v>
-      </c>
-      <c r="C8" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409545&amp;sid=a2e881787d5869f0ba0591995121c6bf</v>
-      </c>
-      <c r="D8" t="str">
-        <v>2026-02-09</v>
-      </c>
-      <c r="E8" t="str">
-        <v/>
-      </c>
-      <c r="F8" t="str">
-        <v/>
-      </c>
-      <c r="G8" t="str">
-        <v/>
-      </c>
-      <c r="H8" t="str">
-        <v/>
-      </c>
-      <c r="I8" t="str">
-        <v>סינגלים חדשים</v>
-      </c>
-      <c r="J8" t="str">
-        <v/>
-      </c>
-      <c r="K8" t="str">
-        <v/>
-      </c>
-      <c r="L8" t="str">
-        <v>אליעד &amp; לירון עמרם - עוד שבוע</v>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" t="str">
-        <v>אביה שרמן &amp; אביעד - משיח</v>
-      </c>
-      <c r="B9" t="str">
-        <v>2026-02-09</v>
-      </c>
-      <c r="C9" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409544&amp;sid=a2e881787d5869f0ba0591995121c6bf</v>
-      </c>
-      <c r="D9" t="str">
-        <v>2026-02-09</v>
-      </c>
-      <c r="E9" t="str">
-        <v/>
-      </c>
-      <c r="F9" t="str">
-        <v/>
-      </c>
-      <c r="G9" t="str">
-        <v/>
-      </c>
-      <c r="H9" t="str">
-        <v/>
-      </c>
-      <c r="I9" t="str">
-        <v>סינגלים חדשים</v>
-      </c>
-      <c r="J9" t="str">
-        <v/>
-      </c>
-      <c r="K9" t="str">
-        <v/>
-      </c>
-      <c r="L9" t="str">
-        <v>אביה שרמן &amp; אביעד - משיח</v>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" t="str">
-        <v>מיסטר הבי ומיס לואו – Not everything you wanted</v>
-      </c>
-      <c r="B10" t="str">
-        <v>2026-02-09</v>
-      </c>
-      <c r="C10" t="str">
-        <v>https://yosmusic.com/%d7%9e%d7%99%d7%a1%d7%98%d7%a8-%d7%94%d7%91%d7%99-%d7%95%d7%9e%d7%99%d7%a1-%d7%9c%d7%95%d7%90%d7%95-not-everything-you-wanted/</v>
-      </c>
-      <c r="D10" t="str">
-        <v>2026-02-09</v>
-      </c>
-      <c r="E10" t="str">
-        <v/>
-      </c>
-      <c r="F10" t="str">
-        <v>. “Not Everything You Wanted” של מיסטר הבי אנד מיס לואו (Mr. Heavy &amp; Ms. Low) הוא שיר מעבר  לא רק גיאוגרפי (עיר-כפר), אלא קיומי. שיר על בחירה שמכילה ויתור, אימהות בלי אידיאליזציה, חיים כפריים כמרחב של גילוי, לא של</v>
-      </c>
-      <c r="G10" t="str">
-        <v/>
-      </c>
-      <c r="H10" t="str">
-        <v/>
-      </c>
-      <c r="I10" t="str">
-        <v>סינגלים חדשים</v>
-      </c>
-      <c r="J10" t="str">
-        <v/>
-      </c>
-      <c r="K10" t="str">
-        <v/>
-      </c>
-      <c r="L10" t="str">
-        <v>מיסטר הבי ומיס לואו – Not everything you wanted</v>
+        <v>איציק קלה &amp; יובל טייב - רפאני</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:L10"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:L2"/>
   </ignoredErrors>
 </worksheet>
 </file>
--- a/data/tags/סינגלים חדשים/global/2026-02-week02/titles.xlsx
+++ b/data/tags/סינגלים חדשים/global/2026-02-week02/titles.xlsx
@@ -397,7 +397,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:L2"/>
+  <dimension ref="A1:L14"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -436,16 +436,16 @@
     </row>
     <row r="2">
       <c r="A2" t="str">
-        <v>איציק קלה &amp; יובל טייב - רפאני</v>
+        <v>חזי פניאן - מתל אביב לטהרן</v>
       </c>
       <c r="B2" t="str">
-        <v>2026-02-09</v>
+        <v>2026-02-10</v>
       </c>
       <c r="C2" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=383792&amp;sid=adb305d69ff5373f52ea1464f61a4067</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409563&amp;sid=1d9a579b64f7454a0d6e1ca1a25e92d9</v>
       </c>
       <c r="D2" t="str">
-        <v>2026-02-09</v>
+        <v>2026-02-10</v>
       </c>
       <c r="E2" t="str">
         <v/>
@@ -469,12 +469,468 @@
         <v/>
       </c>
       <c r="L2" t="str">
-        <v>איציק קלה &amp; יובל טייב - רפאני</v>
+        <v>חזי פניאן - מתל אביב לטהרן</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="str">
+        <v>הנסיך מהמזרח - מחרוזת דיכאון חלק א 2026</v>
+      </c>
+      <c r="B3" t="str">
+        <v>2026-02-10</v>
+      </c>
+      <c r="C3" t="str">
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409562&amp;sid=1d9a579b64f7454a0d6e1ca1a25e92d9</v>
+      </c>
+      <c r="D3" t="str">
+        <v>2026-02-10</v>
+      </c>
+      <c r="E3" t="str">
+        <v/>
+      </c>
+      <c r="F3" t="str">
+        <v/>
+      </c>
+      <c r="G3" t="str">
+        <v/>
+      </c>
+      <c r="H3" t="str">
+        <v/>
+      </c>
+      <c r="I3" t="str">
+        <v>סינגלים חדשים</v>
+      </c>
+      <c r="J3" t="str">
+        <v/>
+      </c>
+      <c r="K3" t="str">
+        <v/>
+      </c>
+      <c r="L3" t="str">
+        <v>הנסיך מהמזרח - מחרוזת דיכאון חלק א 2026</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="str">
+        <v>דוד ירושלמי - טעם מר</v>
+      </c>
+      <c r="B4" t="str">
+        <v>2026-02-10</v>
+      </c>
+      <c r="C4" t="str">
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409561&amp;sid=1d9a579b64f7454a0d6e1ca1a25e92d9</v>
+      </c>
+      <c r="D4" t="str">
+        <v>2026-02-10</v>
+      </c>
+      <c r="E4" t="str">
+        <v/>
+      </c>
+      <c r="F4" t="str">
+        <v/>
+      </c>
+      <c r="G4" t="str">
+        <v/>
+      </c>
+      <c r="H4" t="str">
+        <v/>
+      </c>
+      <c r="I4" t="str">
+        <v>סינגלים חדשים</v>
+      </c>
+      <c r="J4" t="str">
+        <v/>
+      </c>
+      <c r="K4" t="str">
+        <v/>
+      </c>
+      <c r="L4" t="str">
+        <v>דוד ירושלמי - טעם מר</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="str">
+        <v>גיל ואזנה - בני (לא) ילד רע</v>
+      </c>
+      <c r="B5" t="str">
+        <v>2026-02-10</v>
+      </c>
+      <c r="C5" t="str">
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409560&amp;sid=1d9a579b64f7454a0d6e1ca1a25e92d9</v>
+      </c>
+      <c r="D5" t="str">
+        <v>2026-02-10</v>
+      </c>
+      <c r="E5" t="str">
+        <v/>
+      </c>
+      <c r="F5" t="str">
+        <v/>
+      </c>
+      <c r="G5" t="str">
+        <v/>
+      </c>
+      <c r="H5" t="str">
+        <v/>
+      </c>
+      <c r="I5" t="str">
+        <v>סינגלים חדשים</v>
+      </c>
+      <c r="J5" t="str">
+        <v/>
+      </c>
+      <c r="K5" t="str">
+        <v/>
+      </c>
+      <c r="L5" t="str">
+        <v>גיל ואזנה - בני (לא) ילד רע</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="str">
+        <v>אלייצור &amp; ששון שאולוב - אחותי</v>
+      </c>
+      <c r="B6" t="str">
+        <v>2026-02-10</v>
+      </c>
+      <c r="C6" t="str">
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409559&amp;sid=1d9a579b64f7454a0d6e1ca1a25e92d9</v>
+      </c>
+      <c r="D6" t="str">
+        <v>2026-02-10</v>
+      </c>
+      <c r="E6" t="str">
+        <v/>
+      </c>
+      <c r="F6" t="str">
+        <v/>
+      </c>
+      <c r="G6" t="str">
+        <v/>
+      </c>
+      <c r="H6" t="str">
+        <v/>
+      </c>
+      <c r="I6" t="str">
+        <v>סינגלים חדשים</v>
+      </c>
+      <c r="J6" t="str">
+        <v/>
+      </c>
+      <c r="K6" t="str">
+        <v/>
+      </c>
+      <c r="L6" t="str">
+        <v>אלייצור &amp; ששון שאולוב - אחותי</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="str">
+        <v>אליאור אלון - מחרוזת לא אשכח את הילדות 2026</v>
+      </c>
+      <c r="B7" t="str">
+        <v>2026-02-10</v>
+      </c>
+      <c r="C7" t="str">
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409558&amp;sid=1d9a579b64f7454a0d6e1ca1a25e92d9</v>
+      </c>
+      <c r="D7" t="str">
+        <v>2026-02-10</v>
+      </c>
+      <c r="E7" t="str">
+        <v/>
+      </c>
+      <c r="F7" t="str">
+        <v/>
+      </c>
+      <c r="G7" t="str">
+        <v/>
+      </c>
+      <c r="H7" t="str">
+        <v/>
+      </c>
+      <c r="I7" t="str">
+        <v>סינגלים חדשים</v>
+      </c>
+      <c r="J7" t="str">
+        <v/>
+      </c>
+      <c r="K7" t="str">
+        <v/>
+      </c>
+      <c r="L7" t="str">
+        <v>אליאור אלון - מחרוזת לא אשכח את הילדות 2026</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="str">
+        <v>אלי אליאב - מחרוזת כאב ואכזבות 2026</v>
+      </c>
+      <c r="B8" t="str">
+        <v>2026-02-10</v>
+      </c>
+      <c r="C8" t="str">
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409557&amp;sid=1d9a579b64f7454a0d6e1ca1a25e92d9</v>
+      </c>
+      <c r="D8" t="str">
+        <v>2026-02-10</v>
+      </c>
+      <c r="E8" t="str">
+        <v/>
+      </c>
+      <c r="F8" t="str">
+        <v/>
+      </c>
+      <c r="G8" t="str">
+        <v/>
+      </c>
+      <c r="H8" t="str">
+        <v/>
+      </c>
+      <c r="I8" t="str">
+        <v>סינגלים חדשים</v>
+      </c>
+      <c r="J8" t="str">
+        <v/>
+      </c>
+      <c r="K8" t="str">
+        <v/>
+      </c>
+      <c r="L8" t="str">
+        <v>אלי אליאב - מחרוזת כאב ואכזבות 2026</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="str">
+        <v>איתמר הרוש - לוקה</v>
+      </c>
+      <c r="B9" t="str">
+        <v>2026-02-10</v>
+      </c>
+      <c r="C9" t="str">
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409556&amp;sid=1d9a579b64f7454a0d6e1ca1a25e92d9</v>
+      </c>
+      <c r="D9" t="str">
+        <v>2026-02-10</v>
+      </c>
+      <c r="E9" t="str">
+        <v/>
+      </c>
+      <c r="F9" t="str">
+        <v/>
+      </c>
+      <c r="G9" t="str">
+        <v/>
+      </c>
+      <c r="H9" t="str">
+        <v/>
+      </c>
+      <c r="I9" t="str">
+        <v>סינגלים חדשים</v>
+      </c>
+      <c r="J9" t="str">
+        <v/>
+      </c>
+      <c r="K9" t="str">
+        <v/>
+      </c>
+      <c r="L9" t="str">
+        <v>איתמר הרוש - לוקה</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="str">
+        <v>איתי גל מארח את יהודה קיסר - מה בא לך</v>
+      </c>
+      <c r="B10" t="str">
+        <v>2026-02-10</v>
+      </c>
+      <c r="C10" t="str">
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409555&amp;sid=1d9a579b64f7454a0d6e1ca1a25e92d9</v>
+      </c>
+      <c r="D10" t="str">
+        <v>2026-02-10</v>
+      </c>
+      <c r="E10" t="str">
+        <v/>
+      </c>
+      <c r="F10" t="str">
+        <v/>
+      </c>
+      <c r="G10" t="str">
+        <v/>
+      </c>
+      <c r="H10" t="str">
+        <v/>
+      </c>
+      <c r="I10" t="str">
+        <v>סינגלים חדשים</v>
+      </c>
+      <c r="J10" t="str">
+        <v/>
+      </c>
+      <c r="K10" t="str">
+        <v/>
+      </c>
+      <c r="L10" t="str">
+        <v>איתי גל מארח את יהודה קיסר - מה בא לך</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="str">
+        <v>אוראל פרג׳ - מאשאפ דיכאון 2026</v>
+      </c>
+      <c r="B11" t="str">
+        <v>2026-02-10</v>
+      </c>
+      <c r="C11" t="str">
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409554&amp;sid=1d9a579b64f7454a0d6e1ca1a25e92d9</v>
+      </c>
+      <c r="D11" t="str">
+        <v>2026-02-10</v>
+      </c>
+      <c r="E11" t="str">
+        <v/>
+      </c>
+      <c r="F11" t="str">
+        <v/>
+      </c>
+      <c r="G11" t="str">
+        <v/>
+      </c>
+      <c r="H11" t="str">
+        <v/>
+      </c>
+      <c r="I11" t="str">
+        <v>סינגלים חדשים</v>
+      </c>
+      <c r="J11" t="str">
+        <v/>
+      </c>
+      <c r="K11" t="str">
+        <v/>
+      </c>
+      <c r="L11" t="str">
+        <v>אוראל פרג׳ - מאשאפ דיכאון 2026</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="str">
+        <v>אופיר נגר - מחרוזת חפלה ערבית טורקית 2026</v>
+      </c>
+      <c r="B12" t="str">
+        <v>2026-02-10</v>
+      </c>
+      <c r="C12" t="str">
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409553&amp;sid=1d9a579b64f7454a0d6e1ca1a25e92d9</v>
+      </c>
+      <c r="D12" t="str">
+        <v>2026-02-10</v>
+      </c>
+      <c r="E12" t="str">
+        <v/>
+      </c>
+      <c r="F12" t="str">
+        <v/>
+      </c>
+      <c r="G12" t="str">
+        <v/>
+      </c>
+      <c r="H12" t="str">
+        <v/>
+      </c>
+      <c r="I12" t="str">
+        <v>סינגלים חדשים</v>
+      </c>
+      <c r="J12" t="str">
+        <v/>
+      </c>
+      <c r="K12" t="str">
+        <v/>
+      </c>
+      <c r="L12" t="str">
+        <v>אופיר נגר - מחרוזת חפלה ערבית טורקית 2026</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="str">
+        <v>אבירם עמר - חץ וסוכריה</v>
+      </c>
+      <c r="B13" t="str">
+        <v>2026-02-10</v>
+      </c>
+      <c r="C13" t="str">
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409552&amp;sid=1d9a579b64f7454a0d6e1ca1a25e92d9</v>
+      </c>
+      <c r="D13" t="str">
+        <v>2026-02-10</v>
+      </c>
+      <c r="E13" t="str">
+        <v/>
+      </c>
+      <c r="F13" t="str">
+        <v/>
+      </c>
+      <c r="G13" t="str">
+        <v/>
+      </c>
+      <c r="H13" t="str">
+        <v/>
+      </c>
+      <c r="I13" t="str">
+        <v>סינגלים חדשים</v>
+      </c>
+      <c r="J13" t="str">
+        <v/>
+      </c>
+      <c r="K13" t="str">
+        <v/>
+      </c>
+      <c r="L13" t="str">
+        <v>אבירם עמר - חץ וסוכריה</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="str">
+        <v>שלומי שבן אלון עדר – עברנו לצפון קרית שמונה</v>
+      </c>
+      <c r="B14" t="str">
+        <v>2026-02-10</v>
+      </c>
+      <c r="C14" t="str">
+        <v>https://yosmusic.com/%d7%a9%d7%9c%d7%95%d7%9e%d7%99-%d7%a9%d7%91%d7%9f-%d7%90%d7%9c%d7%95%d7%9f-%d7%a2%d7%93%d7%a8-%d7%a2%d7%91%d7%a8%d7%a0%d7%95-%d7%9c%d7%a6%d7%a4%d7%95%d7%9f-%d7%a7%d7%a8%d7%99%d7%aa-%d7%a9%d7%9e%d7%95/</v>
+      </c>
+      <c r="D14" t="str">
+        <v>2026-02-10</v>
+      </c>
+      <c r="E14" t="str">
+        <v/>
+      </c>
+      <c r="F14" t="str">
+        <v>אני מנסה לקרוא/ לחוש מאת המשאפ הזה בין שלומי שבן ואלון עדר לא רק כחיבור טכני בין שני שירים – אלא כטקסט אחד שמספר סיפור עם התפתחות רגשית ומוזיקלית. החיבור בין "עברנו לצפון” (שלומי שבן) ל־"קריית שמונה” (אלון עדר) מנסה</v>
+      </c>
+      <c r="G14" t="str">
+        <v/>
+      </c>
+      <c r="H14" t="str">
+        <v/>
+      </c>
+      <c r="I14" t="str">
+        <v>סינגלים חדשים</v>
+      </c>
+      <c r="J14" t="str">
+        <v/>
+      </c>
+      <c r="K14" t="str">
+        <v/>
+      </c>
+      <c r="L14" t="str">
+        <v>שלומי שבן אלון עדר – עברנו לצפון קרית שמונה</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:L2"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:L14"/>
   </ignoredErrors>
 </worksheet>
 </file>
--- a/data/tags/סינגלים חדשים/global/2026-02-week02/titles.xlsx
+++ b/data/tags/סינגלים חדשים/global/2026-02-week02/titles.xlsx
@@ -397,7 +397,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:L14"/>
+  <dimension ref="A1:L5"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -436,13 +436,13 @@
     </row>
     <row r="2">
       <c r="A2" t="str">
-        <v>חזי פניאן - מתל אביב לטהרן</v>
+        <v>משה גנון - דרמה</v>
       </c>
       <c r="B2" t="str">
         <v>2026-02-10</v>
       </c>
       <c r="C2" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409563&amp;sid=1d9a579b64f7454a0d6e1ca1a25e92d9</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409567&amp;sid=fab2598180a774363108ef750cff9054</v>
       </c>
       <c r="D2" t="str">
         <v>2026-02-10</v>
@@ -469,18 +469,18 @@
         <v/>
       </c>
       <c r="L2" t="str">
-        <v>חזי פניאן - מתל אביב לטהרן</v>
+        <v>משה גנון - דרמה</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="str">
-        <v>הנסיך מהמזרח - מחרוזת דיכאון חלק א 2026</v>
+        <v>לידור יוספי &amp; שטובי - הבוטח בה'</v>
       </c>
       <c r="B3" t="str">
         <v>2026-02-10</v>
       </c>
       <c r="C3" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409562&amp;sid=1d9a579b64f7454a0d6e1ca1a25e92d9</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409566&amp;sid=fab2598180a774363108ef750cff9054</v>
       </c>
       <c r="D3" t="str">
         <v>2026-02-10</v>
@@ -507,18 +507,18 @@
         <v/>
       </c>
       <c r="L3" t="str">
-        <v>הנסיך מהמזרח - מחרוזת דיכאון חלק א 2026</v>
+        <v>לידור יוספי &amp; שטובי - הבוטח בה'</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="str">
-        <v>דוד ירושלמי - טעם מר</v>
+        <v>ליאור ברגר - אם רק תגידי כן</v>
       </c>
       <c r="B4" t="str">
         <v>2026-02-10</v>
       </c>
       <c r="C4" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409561&amp;sid=1d9a579b64f7454a0d6e1ca1a25e92d9</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409565&amp;sid=fab2598180a774363108ef750cff9054</v>
       </c>
       <c r="D4" t="str">
         <v>2026-02-10</v>
@@ -545,18 +545,18 @@
         <v/>
       </c>
       <c r="L4" t="str">
-        <v>דוד ירושלמי - טעם מר</v>
+        <v>ליאור ברגר - אם רק תגידי כן</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="str">
-        <v>גיל ואזנה - בני (לא) ילד רע</v>
+        <v>חן אלדטוב - לרקוד על הכאב</v>
       </c>
       <c r="B5" t="str">
         <v>2026-02-10</v>
       </c>
       <c r="C5" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409560&amp;sid=1d9a579b64f7454a0d6e1ca1a25e92d9</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409564&amp;sid=fab2598180a774363108ef750cff9054</v>
       </c>
       <c r="D5" t="str">
         <v>2026-02-10</v>
@@ -583,354 +583,12 @@
         <v/>
       </c>
       <c r="L5" t="str">
-        <v>גיל ואזנה - בני (לא) ילד רע</v>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" t="str">
-        <v>אלייצור &amp; ששון שאולוב - אחותי</v>
-      </c>
-      <c r="B6" t="str">
-        <v>2026-02-10</v>
-      </c>
-      <c r="C6" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409559&amp;sid=1d9a579b64f7454a0d6e1ca1a25e92d9</v>
-      </c>
-      <c r="D6" t="str">
-        <v>2026-02-10</v>
-      </c>
-      <c r="E6" t="str">
-        <v/>
-      </c>
-      <c r="F6" t="str">
-        <v/>
-      </c>
-      <c r="G6" t="str">
-        <v/>
-      </c>
-      <c r="H6" t="str">
-        <v/>
-      </c>
-      <c r="I6" t="str">
-        <v>סינגלים חדשים</v>
-      </c>
-      <c r="J6" t="str">
-        <v/>
-      </c>
-      <c r="K6" t="str">
-        <v/>
-      </c>
-      <c r="L6" t="str">
-        <v>אלייצור &amp; ששון שאולוב - אחותי</v>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" t="str">
-        <v>אליאור אלון - מחרוזת לא אשכח את הילדות 2026</v>
-      </c>
-      <c r="B7" t="str">
-        <v>2026-02-10</v>
-      </c>
-      <c r="C7" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409558&amp;sid=1d9a579b64f7454a0d6e1ca1a25e92d9</v>
-      </c>
-      <c r="D7" t="str">
-        <v>2026-02-10</v>
-      </c>
-      <c r="E7" t="str">
-        <v/>
-      </c>
-      <c r="F7" t="str">
-        <v/>
-      </c>
-      <c r="G7" t="str">
-        <v/>
-      </c>
-      <c r="H7" t="str">
-        <v/>
-      </c>
-      <c r="I7" t="str">
-        <v>סינגלים חדשים</v>
-      </c>
-      <c r="J7" t="str">
-        <v/>
-      </c>
-      <c r="K7" t="str">
-        <v/>
-      </c>
-      <c r="L7" t="str">
-        <v>אליאור אלון - מחרוזת לא אשכח את הילדות 2026</v>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" t="str">
-        <v>אלי אליאב - מחרוזת כאב ואכזבות 2026</v>
-      </c>
-      <c r="B8" t="str">
-        <v>2026-02-10</v>
-      </c>
-      <c r="C8" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409557&amp;sid=1d9a579b64f7454a0d6e1ca1a25e92d9</v>
-      </c>
-      <c r="D8" t="str">
-        <v>2026-02-10</v>
-      </c>
-      <c r="E8" t="str">
-        <v/>
-      </c>
-      <c r="F8" t="str">
-        <v/>
-      </c>
-      <c r="G8" t="str">
-        <v/>
-      </c>
-      <c r="H8" t="str">
-        <v/>
-      </c>
-      <c r="I8" t="str">
-        <v>סינגלים חדשים</v>
-      </c>
-      <c r="J8" t="str">
-        <v/>
-      </c>
-      <c r="K8" t="str">
-        <v/>
-      </c>
-      <c r="L8" t="str">
-        <v>אלי אליאב - מחרוזת כאב ואכזבות 2026</v>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" t="str">
-        <v>איתמר הרוש - לוקה</v>
-      </c>
-      <c r="B9" t="str">
-        <v>2026-02-10</v>
-      </c>
-      <c r="C9" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409556&amp;sid=1d9a579b64f7454a0d6e1ca1a25e92d9</v>
-      </c>
-      <c r="D9" t="str">
-        <v>2026-02-10</v>
-      </c>
-      <c r="E9" t="str">
-        <v/>
-      </c>
-      <c r="F9" t="str">
-        <v/>
-      </c>
-      <c r="G9" t="str">
-        <v/>
-      </c>
-      <c r="H9" t="str">
-        <v/>
-      </c>
-      <c r="I9" t="str">
-        <v>סינגלים חדשים</v>
-      </c>
-      <c r="J9" t="str">
-        <v/>
-      </c>
-      <c r="K9" t="str">
-        <v/>
-      </c>
-      <c r="L9" t="str">
-        <v>איתמר הרוש - לוקה</v>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" t="str">
-        <v>איתי גל מארח את יהודה קיסר - מה בא לך</v>
-      </c>
-      <c r="B10" t="str">
-        <v>2026-02-10</v>
-      </c>
-      <c r="C10" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409555&amp;sid=1d9a579b64f7454a0d6e1ca1a25e92d9</v>
-      </c>
-      <c r="D10" t="str">
-        <v>2026-02-10</v>
-      </c>
-      <c r="E10" t="str">
-        <v/>
-      </c>
-      <c r="F10" t="str">
-        <v/>
-      </c>
-      <c r="G10" t="str">
-        <v/>
-      </c>
-      <c r="H10" t="str">
-        <v/>
-      </c>
-      <c r="I10" t="str">
-        <v>סינגלים חדשים</v>
-      </c>
-      <c r="J10" t="str">
-        <v/>
-      </c>
-      <c r="K10" t="str">
-        <v/>
-      </c>
-      <c r="L10" t="str">
-        <v>איתי גל מארח את יהודה קיסר - מה בא לך</v>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" t="str">
-        <v>אוראל פרג׳ - מאשאפ דיכאון 2026</v>
-      </c>
-      <c r="B11" t="str">
-        <v>2026-02-10</v>
-      </c>
-      <c r="C11" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409554&amp;sid=1d9a579b64f7454a0d6e1ca1a25e92d9</v>
-      </c>
-      <c r="D11" t="str">
-        <v>2026-02-10</v>
-      </c>
-      <c r="E11" t="str">
-        <v/>
-      </c>
-      <c r="F11" t="str">
-        <v/>
-      </c>
-      <c r="G11" t="str">
-        <v/>
-      </c>
-      <c r="H11" t="str">
-        <v/>
-      </c>
-      <c r="I11" t="str">
-        <v>סינגלים חדשים</v>
-      </c>
-      <c r="J11" t="str">
-        <v/>
-      </c>
-      <c r="K11" t="str">
-        <v/>
-      </c>
-      <c r="L11" t="str">
-        <v>אוראל פרג׳ - מאשאפ דיכאון 2026</v>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" t="str">
-        <v>אופיר נגר - מחרוזת חפלה ערבית טורקית 2026</v>
-      </c>
-      <c r="B12" t="str">
-        <v>2026-02-10</v>
-      </c>
-      <c r="C12" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409553&amp;sid=1d9a579b64f7454a0d6e1ca1a25e92d9</v>
-      </c>
-      <c r="D12" t="str">
-        <v>2026-02-10</v>
-      </c>
-      <c r="E12" t="str">
-        <v/>
-      </c>
-      <c r="F12" t="str">
-        <v/>
-      </c>
-      <c r="G12" t="str">
-        <v/>
-      </c>
-      <c r="H12" t="str">
-        <v/>
-      </c>
-      <c r="I12" t="str">
-        <v>סינגלים חדשים</v>
-      </c>
-      <c r="J12" t="str">
-        <v/>
-      </c>
-      <c r="K12" t="str">
-        <v/>
-      </c>
-      <c r="L12" t="str">
-        <v>אופיר נגר - מחרוזת חפלה ערבית טורקית 2026</v>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" t="str">
-        <v>אבירם עמר - חץ וסוכריה</v>
-      </c>
-      <c r="B13" t="str">
-        <v>2026-02-10</v>
-      </c>
-      <c r="C13" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409552&amp;sid=1d9a579b64f7454a0d6e1ca1a25e92d9</v>
-      </c>
-      <c r="D13" t="str">
-        <v>2026-02-10</v>
-      </c>
-      <c r="E13" t="str">
-        <v/>
-      </c>
-      <c r="F13" t="str">
-        <v/>
-      </c>
-      <c r="G13" t="str">
-        <v/>
-      </c>
-      <c r="H13" t="str">
-        <v/>
-      </c>
-      <c r="I13" t="str">
-        <v>סינגלים חדשים</v>
-      </c>
-      <c r="J13" t="str">
-        <v/>
-      </c>
-      <c r="K13" t="str">
-        <v/>
-      </c>
-      <c r="L13" t="str">
-        <v>אבירם עמר - חץ וסוכריה</v>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" t="str">
-        <v>שלומי שבן אלון עדר – עברנו לצפון קרית שמונה</v>
-      </c>
-      <c r="B14" t="str">
-        <v>2026-02-10</v>
-      </c>
-      <c r="C14" t="str">
-        <v>https://yosmusic.com/%d7%a9%d7%9c%d7%95%d7%9e%d7%99-%d7%a9%d7%91%d7%9f-%d7%90%d7%9c%d7%95%d7%9f-%d7%a2%d7%93%d7%a8-%d7%a2%d7%91%d7%a8%d7%a0%d7%95-%d7%9c%d7%a6%d7%a4%d7%95%d7%9f-%d7%a7%d7%a8%d7%99%d7%aa-%d7%a9%d7%9e%d7%95/</v>
-      </c>
-      <c r="D14" t="str">
-        <v>2026-02-10</v>
-      </c>
-      <c r="E14" t="str">
-        <v/>
-      </c>
-      <c r="F14" t="str">
-        <v>אני מנסה לקרוא/ לחוש מאת המשאפ הזה בין שלומי שבן ואלון עדר לא רק כחיבור טכני בין שני שירים – אלא כטקסט אחד שמספר סיפור עם התפתחות רגשית ומוזיקלית. החיבור בין "עברנו לצפון” (שלומי שבן) ל־"קריית שמונה” (אלון עדר) מנסה</v>
-      </c>
-      <c r="G14" t="str">
-        <v/>
-      </c>
-      <c r="H14" t="str">
-        <v/>
-      </c>
-      <c r="I14" t="str">
-        <v>סינגלים חדשים</v>
-      </c>
-      <c r="J14" t="str">
-        <v/>
-      </c>
-      <c r="K14" t="str">
-        <v/>
-      </c>
-      <c r="L14" t="str">
-        <v>שלומי שבן אלון עדר – עברנו לצפון קרית שמונה</v>
+        <v>חן אלדטוב - לרקוד על הכאב</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:L14"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:L5"/>
   </ignoredErrors>
 </worksheet>
 </file>
--- a/data/tags/סינגלים חדשים/global/2026-02-week02/titles.xlsx
+++ b/data/tags/סינגלים חדשים/global/2026-02-week02/titles.xlsx
@@ -397,7 +397,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:L5"/>
+  <dimension ref="A1:L4"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -436,13 +436,13 @@
     </row>
     <row r="2">
       <c r="A2" t="str">
-        <v>משה גנון - דרמה</v>
+        <v>שיר אוזן - לא להפסיד לך</v>
       </c>
       <c r="B2" t="str">
         <v>2026-02-10</v>
       </c>
       <c r="C2" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409567&amp;sid=fab2598180a774363108ef750cff9054</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409570&amp;sid=c3a718fc81c2ca72e382a9c8f97d80a4</v>
       </c>
       <c r="D2" t="str">
         <v>2026-02-10</v>
@@ -469,18 +469,18 @@
         <v/>
       </c>
       <c r="L2" t="str">
-        <v>משה גנון - דרמה</v>
+        <v>שיר אוזן - לא להפסיד לך</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="str">
-        <v>לידור יוספי &amp; שטובי - הבוטח בה'</v>
+        <v>רואי אדם - אהבת חיי</v>
       </c>
       <c r="B3" t="str">
         <v>2026-02-10</v>
       </c>
       <c r="C3" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409566&amp;sid=fab2598180a774363108ef750cff9054</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409569&amp;sid=c3a718fc81c2ca72e382a9c8f97d80a4</v>
       </c>
       <c r="D3" t="str">
         <v>2026-02-10</v>
@@ -507,18 +507,18 @@
         <v/>
       </c>
       <c r="L3" t="str">
-        <v>לידור יוספי &amp; שטובי - הבוטח בה'</v>
+        <v>רואי אדם - אהבת חיי</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="str">
-        <v>ליאור ברגר - אם רק תגידי כן</v>
+        <v>ניצן אלון - לפני שלושים</v>
       </c>
       <c r="B4" t="str">
         <v>2026-02-10</v>
       </c>
       <c r="C4" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409565&amp;sid=fab2598180a774363108ef750cff9054</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409568&amp;sid=c3a718fc81c2ca72e382a9c8f97d80a4</v>
       </c>
       <c r="D4" t="str">
         <v>2026-02-10</v>
@@ -545,50 +545,12 @@
         <v/>
       </c>
       <c r="L4" t="str">
-        <v>ליאור ברגר - אם רק תגידי כן</v>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" t="str">
-        <v>חן אלדטוב - לרקוד על הכאב</v>
-      </c>
-      <c r="B5" t="str">
-        <v>2026-02-10</v>
-      </c>
-      <c r="C5" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409564&amp;sid=fab2598180a774363108ef750cff9054</v>
-      </c>
-      <c r="D5" t="str">
-        <v>2026-02-10</v>
-      </c>
-      <c r="E5" t="str">
-        <v/>
-      </c>
-      <c r="F5" t="str">
-        <v/>
-      </c>
-      <c r="G5" t="str">
-        <v/>
-      </c>
-      <c r="H5" t="str">
-        <v/>
-      </c>
-      <c r="I5" t="str">
-        <v>סינגלים חדשים</v>
-      </c>
-      <c r="J5" t="str">
-        <v/>
-      </c>
-      <c r="K5" t="str">
-        <v/>
-      </c>
-      <c r="L5" t="str">
-        <v>חן אלדטוב - לרקוד על הכאב</v>
+        <v>ניצן אלון - לפני שלושים</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:L5"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:L4"/>
   </ignoredErrors>
 </worksheet>
 </file>
--- a/data/tags/סינגלים חדשים/global/2026-02-week02/titles.xlsx
+++ b/data/tags/סינגלים חדשים/global/2026-02-week02/titles.xlsx
@@ -397,7 +397,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:L4"/>
+  <dimension ref="A1:L2"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -436,13 +436,13 @@
     </row>
     <row r="2">
       <c r="A2" t="str">
-        <v>שיר אוזן - לא להפסיד לך</v>
+        <v>שירז אברהם - חושך</v>
       </c>
       <c r="B2" t="str">
         <v>2026-02-10</v>
       </c>
       <c r="C2" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409570&amp;sid=c3a718fc81c2ca72e382a9c8f97d80a4</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409571&amp;sid=107ae0d36c82a37240c0a52fbddafdb6</v>
       </c>
       <c r="D2" t="str">
         <v>2026-02-10</v>
@@ -469,88 +469,12 @@
         <v/>
       </c>
       <c r="L2" t="str">
-        <v>שיר אוזן - לא להפסיד לך</v>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" t="str">
-        <v>רואי אדם - אהבת חיי</v>
-      </c>
-      <c r="B3" t="str">
-        <v>2026-02-10</v>
-      </c>
-      <c r="C3" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409569&amp;sid=c3a718fc81c2ca72e382a9c8f97d80a4</v>
-      </c>
-      <c r="D3" t="str">
-        <v>2026-02-10</v>
-      </c>
-      <c r="E3" t="str">
-        <v/>
-      </c>
-      <c r="F3" t="str">
-        <v/>
-      </c>
-      <c r="G3" t="str">
-        <v/>
-      </c>
-      <c r="H3" t="str">
-        <v/>
-      </c>
-      <c r="I3" t="str">
-        <v>סינגלים חדשים</v>
-      </c>
-      <c r="J3" t="str">
-        <v/>
-      </c>
-      <c r="K3" t="str">
-        <v/>
-      </c>
-      <c r="L3" t="str">
-        <v>רואי אדם - אהבת חיי</v>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="str">
-        <v>ניצן אלון - לפני שלושים</v>
-      </c>
-      <c r="B4" t="str">
-        <v>2026-02-10</v>
-      </c>
-      <c r="C4" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409568&amp;sid=c3a718fc81c2ca72e382a9c8f97d80a4</v>
-      </c>
-      <c r="D4" t="str">
-        <v>2026-02-10</v>
-      </c>
-      <c r="E4" t="str">
-        <v/>
-      </c>
-      <c r="F4" t="str">
-        <v/>
-      </c>
-      <c r="G4" t="str">
-        <v/>
-      </c>
-      <c r="H4" t="str">
-        <v/>
-      </c>
-      <c r="I4" t="str">
-        <v>סינגלים חדשים</v>
-      </c>
-      <c r="J4" t="str">
-        <v/>
-      </c>
-      <c r="K4" t="str">
-        <v/>
-      </c>
-      <c r="L4" t="str">
-        <v>ניצן אלון - לפני שלושים</v>
+        <v>שירז אברהם - חושך</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:L4"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:L2"/>
   </ignoredErrors>
 </worksheet>
 </file>